--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92738</v>
+        <v>92741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>135816520</v>
       </c>
       <c r="B8" t="n">
-        <v>92741</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1999,56 +1999,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120865982</v>
+        <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>56925</v>
+        <v>93449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100045</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
+          <t>Hyttens kvarn, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495346</v>
+        <v>495342</v>
       </c>
       <c r="R14" t="n">
-        <v>6389427</v>
+        <v>6389009</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,17 +2062,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Eksjö</t>
+          <t>Höreda</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Observerad av Helena Hillerdal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,33 +2086,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Ellen Lovén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kenneth Gunnarsson</t>
+          <t>Via Ellen Lovén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120865982</t>
+          <t>https://artportalen.se/Sighting/136922095</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633334</v>
+        <v>120865982</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>56925</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,16 +2121,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2142,7 +2143,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2182,12 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,38 +2214,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633334</t>
+          <t>https://artportalen.se/Sighting/120865982</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124593630</v>
+        <v>119633334</v>
       </c>
       <c r="B16" t="n">
-        <v>58541</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102987</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2252,7 +2253,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2292,12 +2293,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,16 +2324,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593630</t>
+          <t>https://artportalen.se/Sighting/119633334</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124593649</v>
+        <v>124593630</v>
       </c>
       <c r="B17" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2433,16 +2434,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593649</t>
+          <t>https://artportalen.se/Sighting/124593630</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124313105</v>
+        <v>124593649</v>
       </c>
       <c r="B18" t="n">
-        <v>58393</v>
+        <v>58497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102999</v>
+        <v>102990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,12 +2513,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,38 +2544,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124313105</t>
+          <t>https://artportalen.se/Sighting/124593649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119780357</v>
+        <v>124313105</v>
       </c>
       <c r="B19" t="n">
-        <v>58327</v>
+        <v>58393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,7 +2583,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2622,12 +2623,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,16 +2654,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119780357</t>
+          <t>https://artportalen.se/Sighting/124313105</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125858799</v>
+        <v>119780357</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,21 +2671,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,7 +2693,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2732,12 +2733,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,38 +2764,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125858799</t>
+          <t>https://artportalen.se/Sighting/119780357</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119513595</v>
+        <v>125858799</v>
       </c>
       <c r="B21" t="n">
-        <v>58112</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2802,7 +2803,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2842,12 +2843,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,16 +2874,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513595</t>
+          <t>https://artportalen.se/Sighting/125858799</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119633360</v>
+        <v>119513595</v>
       </c>
       <c r="B22" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2952,12 +2953,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,38 +2984,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119633360</t>
+          <t>https://artportalen.se/Sighting/119513595</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119513611</v>
+        <v>119633360</v>
       </c>
       <c r="B23" t="n">
-        <v>58602</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,12 +3063,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,33 +3094,33 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119513611</t>
+          <t>https://artportalen.se/Sighting/119633360</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120652960</v>
+        <v>119513611</v>
       </c>
       <c r="B24" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3172,12 +3173,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,38 +3204,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120652960</t>
+          <t>https://artportalen.se/Sighting/119513611</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124593675</v>
+        <v>120652960</v>
       </c>
       <c r="B25" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,7 +3243,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3282,12 +3283,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,33 +3314,33 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124593675</t>
+          <t>https://artportalen.se/Sighting/120652960</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123029820</v>
+        <v>124593675</v>
       </c>
       <c r="B26" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3352,7 +3353,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3392,12 +3393,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,58 +3424,62 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123029820</t>
+          <t>https://artportalen.se/Sighting/124593675</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127748018</v>
+        <v>123029820</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>58085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>205976</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svansjön, Sm</t>
+          <t>Prom tpt kulle Gysjön, Tannarp, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494989</v>
+        <v>495346</v>
       </c>
       <c r="R27" t="n">
-        <v>6389695</v>
+        <v>6389427</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3498,12 +3503,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,34 +3517,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ellen Lovén</t>
+          <t>Kenneth Gunnarsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127748018</t>
+          <t>https://artportalen.se/Sighting/123029820</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135945309</v>
+        <v>127748018</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,17 +3575,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gysjön, Lilla Hässelås, Sm</t>
+          <t>Svansjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495689</v>
+        <v>494989</v>
       </c>
       <c r="R28" t="n">
-        <v>6389419</v>
+        <v>6389695</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3605,12 +3609,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,50 +3641,58 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945309</t>
+          <t>https://artportalen.se/Sighting/127748018</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74499784</v>
+        <v>135945309</v>
       </c>
       <c r="B29" t="n">
-        <v>97977</v>
+        <v>99342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>L15 Hyttens kvarn, Sm</t>
+          <t>Gysjön, Lilla Hässelås, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494934</v>
+        <v>495689</v>
       </c>
       <c r="R29" t="n">
-        <v>6389379</v>
+        <v>6389419</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3704,17 +3716,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,31 +3730,135 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ellen Lovén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135945309</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>74499784</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L15 Hyttens kvarn, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494934</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6389379</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1978-01-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8j 1618. SOM: Huperzia selago. LEG: Allan Karlsson</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Åparti med damm och kärrmark, stig vid åkant bland gran/björk, stenigt</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74499784</t>
         </is>
@@ -3783,6 +3894,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 1084-2023 artfynd.xlsx
+++ b/artfynd/S 1084-2023 artfynd.xlsx
@@ -2002,7 +2002,7 @@
         <v>136922095</v>
       </c>
       <c r="B14" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
